--- a/WorkBot/refactor-experimental/data/orders/Pepsi/Pepsi_Syracuse_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Pepsi/Pepsi_Syracuse_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>CO2 Aluminum Cylinder</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>49.11</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>49.11</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49.11</v>
       </c>
     </row>
     <row r="3">
@@ -477,20 +471,14 @@
           <t>Orange Juice - BIB</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>133.20</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>266.40</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>266.4</v>
       </c>
     </row>
     <row r="4">
@@ -504,20 +492,14 @@
           <t>Lemonade BIB</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>118.00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>118.00</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>118</v>
+      </c>
+      <c r="E4" t="n">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
